--- a/grupos/3ASV - Estadisticos 20211.xlsx
+++ b/grupos/3ASV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="113">
   <si>
     <t>Materia</t>
   </si>
@@ -149,21 +149,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Camarillo Aburto Raymundo</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Camarillo Aburto Raymundo</t>
-  </si>
-  <si>
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
@@ -182,175 +182,175 @@
     <t>APALE</t>
   </si>
   <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>OCAÑA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>TZIZIHUA</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>IRVING</t>
+  </si>
+  <si>
+    <t>OZIEL</t>
+  </si>
+  <si>
+    <t>JAQUELINE</t>
+  </si>
+  <si>
+    <t>DORA LUZ</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
     <t>CANTELLAN</t>
   </si>
   <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MAYA</t>
   </si>
   <si>
     <t>MUÑOZ</t>
   </si>
   <si>
-    <t>OCAÑA</t>
+    <t>NAJERA</t>
   </si>
   <si>
     <t>RIVERA</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>TEPEPA</t>
   </si>
   <si>
     <t>LARA</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>SILVERIO</t>
+  </si>
+  <si>
     <t>CARRILLO</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
+    <t>MONTALVO</t>
   </si>
   <si>
     <t>VARGAS</t>
   </si>
   <si>
-    <t>TLAXCALA</t>
-  </si>
-  <si>
-    <t>TZIZIHUA</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>GUILLERMO SAID</t>
+  </si>
+  <si>
+    <t>DIANA ITZEL</t>
   </si>
   <si>
     <t>DANIELA DEL CARMEN</t>
   </si>
   <si>
+    <t>SURISADAY</t>
+  </si>
+  <si>
+    <t>MARCOS</t>
+  </si>
+  <si>
+    <t>JESUS SAMUEL</t>
+  </si>
+  <si>
+    <t>ROGELIO</t>
+  </si>
+  <si>
+    <t>ARIZBETH</t>
+  </si>
+  <si>
     <t>ANGEL DAVID</t>
   </si>
   <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>IRVING</t>
+    <t>JESUS ANTONIO</t>
+  </si>
+  <si>
+    <t>FRANCISCO YAEL</t>
   </si>
   <si>
     <t>VICTOR HUGO</t>
   </si>
   <si>
-    <t>OZIEL</t>
+    <t>JUAN GUILLERMO</t>
   </si>
   <si>
     <t>KELLY ITZEL</t>
-  </si>
-  <si>
-    <t>JAQUELINE</t>
-  </si>
-  <si>
-    <t>DORA LUZ</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MAYA</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>TEPEPA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>SILVERIO</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>GUILLERMO SAID</t>
-  </si>
-  <si>
-    <t>DIANA ITZEL</t>
-  </si>
-  <si>
-    <t>SURISADAY</t>
-  </si>
-  <si>
-    <t>MARCOS</t>
-  </si>
-  <si>
-    <t>JESUS SAMUEL</t>
-  </si>
-  <si>
-    <t>ROGELIO</t>
-  </si>
-  <si>
-    <t>ARIZBETH</t>
-  </si>
-  <si>
-    <t>JESUS ANTONIO</t>
-  </si>
-  <si>
-    <t>FRANCISCO YAEL</t>
-  </si>
-  <si>
-    <t>JUAN GUILLERMO</t>
   </si>
   <si>
     <t>MICHELLE ROBERTA</t>
@@ -863,19 +863,19 @@
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -911,7 +911,7 @@
         <v>10</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -928,7 +928,7 @@
         <v>-1</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F5">
         <v>7</v>
@@ -949,10 +949,10 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -982,7 +982,7 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -1017,19 +1017,19 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1065,7 +1065,7 @@
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1076,7 +1076,7 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -1094,19 +1094,19 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1130,7 +1130,7 @@
         <v>5</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V7">
         <v>5</v>
@@ -1142,7 +1142,7 @@
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1180,10 +1180,10 @@
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1216,10 +1216,10 @@
         <v>6</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1248,19 +1248,19 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1287,10 +1287,10 @@
         <v>10</v>
       </c>
       <c r="V9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X9">
         <v>10</v>
@@ -1328,16 +1328,16 @@
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1364,10 +1364,10 @@
         <v>8</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1402,19 +1402,19 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1441,16 +1441,16 @@
         <v>8</v>
       </c>
       <c r="V11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1479,19 +1479,19 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1521,13 +1521,13 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>10</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1544,7 +1544,7 @@
         <v>7</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F13">
         <v>8</v>
@@ -1562,13 +1562,13 @@
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1598,7 +1598,7 @@
         <v>7</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>8</v>
@@ -1621,7 +1621,7 @@
         <v>5</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F14">
         <v>7</v>
@@ -1642,10 +1642,10 @@
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1675,7 +1675,7 @@
         <v>5</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>7</v>
@@ -1710,19 +1710,19 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1746,19 +1746,19 @@
         <v>5</v>
       </c>
       <c r="U15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>5</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>10</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1787,19 +1787,19 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1826,16 +1826,16 @@
         <v>8</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1852,7 +1852,7 @@
         <v>5</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F17">
         <v>-1</v>
@@ -1876,7 +1876,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1906,7 +1906,7 @@
         <v>5</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X17">
         <v>-1</v>
@@ -1923,7 +1923,7 @@
         <v>5</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D18">
         <v>7</v>
@@ -1941,19 +1941,19 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1977,19 +1977,19 @@
         <v>5</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>7</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2018,19 +2018,19 @@
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2063,10 +2063,10 @@
         <v>6</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2083,10 +2083,10 @@
         <v>-1</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -2101,13 +2101,13 @@
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2137,10 +2137,10 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y20">
         <v>5</v>
@@ -2151,16 +2151,16 @@
         <v>29</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -2169,10 +2169,10 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2201,19 +2201,19 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2278,19 +2278,19 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2317,7 +2317,7 @@
         <v>8</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W23">
         <v>6</v>
@@ -2326,7 +2326,7 @@
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2343,7 +2343,7 @@
         <v>-1</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F24">
         <v>-1</v>
@@ -2367,7 +2367,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2397,7 +2397,7 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X24">
         <v>-1</v>
@@ -2420,10 +2420,10 @@
         <v>5</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G25">
         <v>5</v>
@@ -2438,13 +2438,13 @@
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2474,10 +2474,10 @@
         <v>5</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y25">
         <v>5</v>
@@ -2536,7 +2536,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>43</v>
@@ -2548,27 +2548,27 @@
         <v>12</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F2">
         <v>57.14</v>
       </c>
       <c r="G2">
-        <v>28.57</v>
+        <v>42.86</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>44</v>
@@ -2577,25 +2577,25 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>57.14</v>
+        <v>61.9</v>
       </c>
       <c r="G3">
-        <v>42.86</v>
+        <v>23.81</v>
       </c>
       <c r="H3">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -2621,7 +2621,7 @@
         <v>38.1</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2632,66 +2632,66 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>46</v>
       </c>
       <c r="C5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>63.64</v>
+        <v>76.19</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>36.36</v>
+        <v>23.81</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>47</v>
       </c>
       <c r="C6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>86.36</v>
+      </c>
+      <c r="G6">
+        <v>13.64</v>
+      </c>
+      <c r="H6">
+        <v>6.6</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>66.67</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>7.8</v>
-      </c>
-      <c r="I6">
-        <v>7</v>
-      </c>
-      <c r="J6">
-        <v>33.33</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -2705,25 +2705,25 @@
         <v>22</v>
       </c>
       <c r="D7">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>77.27</v>
+        <v>90.91</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J7">
-        <v>22.73</v>
+        <v>9.09</v>
       </c>
     </row>
   </sheetData>
@@ -2733,7 +2733,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2768,33 +2768,33 @@
         <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920317</v>
+        <v>20330051920397</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
         <v>46</v>
@@ -2802,421 +2802,161 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920320</v>
+        <v>20330051920328</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920325</v>
+        <v>20330051920328</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920397</v>
+        <v>20330051920330</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920397</v>
+        <v>20330051920330</v>
       </c>
       <c r="B7" t="s">
         <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920328</v>
+        <v>20330051920334</v>
       </c>
       <c r="B8" t="s">
         <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920328</v>
+        <v>20330051920334</v>
       </c>
       <c r="B9" t="s">
         <v>57</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920328</v>
+        <v>20330051920334</v>
       </c>
       <c r="B10" t="s">
         <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920396</v>
+        <v>20330051920335</v>
       </c>
       <c r="B11" t="s">
         <v>58</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920330</v>
-      </c>
-      <c r="B12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920330</v>
-      </c>
-      <c r="B13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" t="s">
-        <v>78</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920330</v>
-      </c>
-      <c r="B14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" t="s">
-        <v>78</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920330</v>
-      </c>
-      <c r="B15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" t="s">
-        <v>78</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>17330051920191</v>
-      </c>
-      <c r="B16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" t="s">
-        <v>69</v>
-      </c>
-      <c r="D16" t="s">
-        <v>79</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>17330051920191</v>
-      </c>
-      <c r="B17" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" t="s">
-        <v>69</v>
-      </c>
-      <c r="D17" t="s">
-        <v>79</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920334</v>
-      </c>
-      <c r="B18" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" t="s">
-        <v>80</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920334</v>
-      </c>
-      <c r="B19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19" t="s">
-        <v>70</v>
-      </c>
-      <c r="D19" t="s">
-        <v>80</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920334</v>
-      </c>
-      <c r="B20" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" t="s">
-        <v>80</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920334</v>
-      </c>
-      <c r="B21" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" t="s">
-        <v>80</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920335</v>
-      </c>
-      <c r="B22" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" t="s">
-        <v>71</v>
-      </c>
-      <c r="D22" t="s">
-        <v>81</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920335</v>
-      </c>
-      <c r="B23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" t="s">
-        <v>71</v>
-      </c>
-      <c r="D23" t="s">
-        <v>81</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920335</v>
-      </c>
-      <c r="B24" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" t="s">
-        <v>71</v>
-      </c>
-      <c r="D24" t="s">
-        <v>81</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
         <v>46</v>
       </c>
     </row>
@@ -3253,183 +2993,183 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920330</v>
+        <v>20330051920334</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920334</v>
+        <v>20330051920328</v>
       </c>
       <c r="B3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" t="s">
         <v>61</v>
       </c>
-      <c r="C3" t="s">
-        <v>70</v>
-      </c>
       <c r="D3" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920328</v>
+        <v>20330051920330</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920335</v>
+        <v>20330051920317</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920317</v>
+        <v>20330051920397</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920397</v>
+        <v>20330051920335</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>17330051920191</v>
+        <v>20330051920318</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920320</v>
+        <v>20330050470026</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920325</v>
+        <v>20330051920320</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920396</v>
+        <v>20330051920321</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920318</v>
+        <v>20330051920322</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
         <v>101</v>
@@ -3440,13 +3180,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330050470026</v>
+        <v>20330051920323</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
         <v>102</v>
@@ -3457,13 +3197,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920321</v>
+        <v>20330051920380</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
         <v>103</v>
@@ -3474,13 +3214,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920322</v>
+        <v>20330051920324</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
         <v>104</v>
@@ -3491,13 +3231,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920323</v>
+        <v>20330051920325</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
         <v>105</v>
@@ -3508,13 +3248,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920380</v>
+        <v>20330051920326</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="D17" t="s">
         <v>106</v>
@@ -3525,13 +3265,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920324</v>
+        <v>20330051920327</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="D18" t="s">
         <v>107</v>
@@ -3542,13 +3282,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920326</v>
+        <v>20330051920396</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D19" t="s">
         <v>108</v>
@@ -3559,13 +3299,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920327</v>
+        <v>20330051920329</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="D20" t="s">
         <v>109</v>
@@ -3576,13 +3316,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920329</v>
+        <v>17330051920191</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s">
         <v>110</v>
@@ -3596,10 +3336,10 @@
         <v>20330051920331</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D22" t="s">
         <v>111</v>
@@ -3613,10 +3353,10 @@
         <v>20330051920333</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D23" t="s">
         <v>112</v>
@@ -3632,7 +3372,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3664,22 +3404,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920326</v>
+        <v>20330051920320</v>
       </c>
       <c r="B2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" t="s">
         <v>88</v>
       </c>
-      <c r="C2" t="s">
-        <v>67</v>
-      </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -3687,22 +3427,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920326</v>
+        <v>20330051920320</v>
       </c>
       <c r="B3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" t="s">
         <v>88</v>
       </c>
-      <c r="C3" t="s">
-        <v>67</v>
-      </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -3710,22 +3450,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920396</v>
+        <v>20330051920325</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -3733,93 +3473,139 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920396</v>
+        <v>20330051920325</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>17330051920191</v>
+        <v>20330051920326</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>17330051920191</v>
+        <v>20330051920326</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920323</v>
+        <v>20330051920396</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
         <v>43</v>
       </c>
       <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920329</v>
+      </c>
+      <c r="B9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" t="s">
+        <v>109</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>17330051920191</v>
+      </c>
+      <c r="B10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" t="s">
+        <v>110</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ASV - Estadisticos 20211.xlsx
+++ b/grupos/3ASV - Estadisticos 20211.xlsx
@@ -940,7 +940,7 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>-1</v>
@@ -976,7 +976,7 @@
         <v>5</v>
       </c>
       <c r="U5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V5">
         <v>-1</v>
@@ -2653,7 +2653,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>5</v>

--- a/grupos/3ASV - Estadisticos 20211.xlsx
+++ b/grupos/3ASV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="113">
   <si>
     <t>Materia</t>
   </si>
@@ -149,15 +149,15 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
+  </si>
+  <si>
     <t>Camarillo Aburto Raymundo</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
-  </si>
-  <si>
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
@@ -182,181 +182,181 @@
     <t>APALE</t>
   </si>
   <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>OCAÑA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>IRVING</t>
+  </si>
+  <si>
+    <t>OZIEL</t>
+  </si>
+  <si>
+    <t>JAQUELINE</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>CANTELLAN</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>IBAÑEZ</t>
   </si>
   <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>OCAÑA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MAYA</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>ESTEVEZ</t>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>TEPEPA</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>SILVERIO</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
   </si>
   <si>
     <t>TZIZIHUA</t>
   </si>
   <si>
-    <t>JOSE MIGUEL</t>
+    <t>GUILLERMO SAID</t>
+  </si>
+  <si>
+    <t>DIANA ITZEL</t>
+  </si>
+  <si>
+    <t>DANIELA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>SURISADAY</t>
+  </si>
+  <si>
+    <t>MARCOS</t>
+  </si>
+  <si>
+    <t>JESUS SAMUEL</t>
+  </si>
+  <si>
+    <t>ROGELIO</t>
+  </si>
+  <si>
+    <t>ARIZBETH</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
   </si>
   <si>
     <t>EMMANUEL</t>
   </si>
   <si>
-    <t>IRVING</t>
-  </si>
-  <si>
-    <t>OZIEL</t>
-  </si>
-  <si>
-    <t>JAQUELINE</t>
+    <t>JESUS ANTONIO</t>
+  </si>
+  <si>
+    <t>FRANCISCO YAEL</t>
+  </si>
+  <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>JUAN GUILLERMO</t>
+  </si>
+  <si>
+    <t>KELLY ITZEL</t>
+  </si>
+  <si>
+    <t>MICHELLE ROBERTA</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
   </si>
   <si>
     <t>DORA LUZ</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>CANTELLAN</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MAYA</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>TEPEPA</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>SILVERIO</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>GUILLERMO SAID</t>
-  </si>
-  <si>
-    <t>DIANA ITZEL</t>
-  </si>
-  <si>
-    <t>DANIELA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>SURISADAY</t>
-  </si>
-  <si>
-    <t>MARCOS</t>
-  </si>
-  <si>
-    <t>JESUS SAMUEL</t>
-  </si>
-  <si>
-    <t>ROGELIO</t>
-  </si>
-  <si>
-    <t>ARIZBETH</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>JESUS ANTONIO</t>
-  </si>
-  <si>
-    <t>FRANCISCO YAEL</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>JUAN GUILLERMO</t>
-  </si>
-  <si>
-    <t>KELLY ITZEL</t>
-  </si>
-  <si>
-    <t>MICHELLE ROBERTA</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
   </si>
 </sst>
 </file>
@@ -860,7 +860,7 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>8</v>
@@ -937,7 +937,7 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>8</v>
@@ -1014,7 +1014,7 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>8</v>
@@ -1050,7 +1050,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>9</v>
@@ -1091,7 +1091,7 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>7</v>
@@ -1127,7 +1127,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U7">
         <v>6</v>
@@ -1168,10 +1168,10 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
         <v>-1</v>
@@ -1207,7 +1207,7 @@
         <v>6</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V8">
         <v>6</v>
@@ -1245,7 +1245,7 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
         <v>9</v>
@@ -1322,10 +1322,10 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
         <v>10</v>
@@ -1361,7 +1361,7 @@
         <v>6</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>9</v>
@@ -1399,7 +1399,7 @@
         <v>6</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I11">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>8</v>
@@ -1476,7 +1476,7 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I12">
         <v>8</v>
@@ -1553,10 +1553,10 @@
         <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <v>-1</v>
@@ -1592,7 +1592,7 @@
         <v>5</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V13">
         <v>7</v>
@@ -1615,7 +1615,7 @@
         <v>5</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <v>5</v>
@@ -1630,10 +1630,10 @@
         <v>5</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
         <v>-1</v>
@@ -1669,7 +1669,7 @@
         <v>5</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V14">
         <v>5</v>
@@ -1707,7 +1707,7 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
         <v>8</v>
@@ -1784,7 +1784,7 @@
         <v>8</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I16">
         <v>8</v>
@@ -1820,7 +1820,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U16">
         <v>8</v>
@@ -1846,7 +1846,7 @@
         <v>5</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D17">
         <v>5</v>
@@ -1861,10 +1861,10 @@
         <v>5</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
         <v>-1</v>
@@ -1900,7 +1900,7 @@
         <v>5</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -1938,7 +1938,7 @@
         <v>9</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I18">
         <v>8</v>
@@ -1974,7 +1974,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U18">
         <v>7</v>
@@ -2015,7 +2015,7 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
         <v>7</v>
@@ -2051,7 +2051,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U19">
         <v>7</v>
@@ -2077,7 +2077,7 @@
         <v>5</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D20">
         <v>-1</v>
@@ -2092,10 +2092,10 @@
         <v>5</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
         <v>-1</v>
@@ -2131,7 +2131,7 @@
         <v>5</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V20">
         <v>-1</v>
@@ -2198,7 +2198,7 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I22">
         <v>8</v>
@@ -2234,7 +2234,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U22">
         <v>8</v>
@@ -2275,7 +2275,7 @@
         <v>9</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I23">
         <v>7</v>
@@ -2311,7 +2311,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U23">
         <v>8</v>
@@ -2337,7 +2337,7 @@
         <v>5</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D24">
         <v>-1</v>
@@ -2352,10 +2352,10 @@
         <v>5</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
         <v>-1</v>
@@ -2391,7 +2391,7 @@
         <v>5</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V24">
         <v>-1</v>
@@ -2414,7 +2414,7 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D25">
         <v>5</v>
@@ -2429,10 +2429,10 @@
         <v>5</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J25">
         <v>-1</v>
@@ -2468,7 +2468,7 @@
         <v>6</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V25">
         <v>5</v>
@@ -2536,7 +2536,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>43</v>
@@ -2545,30 +2545,30 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>57.14</v>
+        <v>61.9</v>
       </c>
       <c r="G2">
-        <v>42.86</v>
+        <v>23.81</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>44</v>
@@ -2580,27 +2580,27 @@
         <v>13</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>61.9</v>
       </c>
       <c r="G3">
-        <v>23.81</v>
+        <v>38.1</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>45</v>
@@ -2609,19 +2609,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>61.9</v>
+        <v>66.67</v>
       </c>
       <c r="G4">
-        <v>38.1</v>
+        <v>33.33</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2641,25 +2641,25 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>80.95</v>
+      </c>
+      <c r="G5">
+        <v>19.05</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>76.19</v>
-      </c>
-      <c r="G5">
+      <c r="J5">
         <v>0</v>
-      </c>
-      <c r="H5">
-        <v>7.8</v>
-      </c>
-      <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>23.81</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -2733,7 +2733,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2768,196 +2768,96 @@
         <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920397</v>
+        <v>20330051920328</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920328</v>
+        <v>20330051920330</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920328</v>
+        <v>20330051920334</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920330</v>
+        <v>20330051920334</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920330</v>
-      </c>
-      <c r="B7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920334</v>
-      </c>
-      <c r="B8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920334</v>
-      </c>
-      <c r="B9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920334</v>
-      </c>
-      <c r="B10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" t="s">
-        <v>63</v>
-      </c>
-      <c r="D10" t="s">
-        <v>69</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920335</v>
-      </c>
-      <c r="B11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" t="s">
-        <v>70</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -2996,64 +2896,64 @@
         <v>20330051920334</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920328</v>
+        <v>20330051920317</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" t="s">
         <v>61</v>
       </c>
-      <c r="D3" t="s">
-        <v>67</v>
-      </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920330</v>
+        <v>20330051920328</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" t="s">
         <v>62</v>
       </c>
-      <c r="D4" t="s">
-        <v>68</v>
-      </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920317</v>
+        <v>20330051920330</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
         <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -3061,47 +2961,47 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920397</v>
+        <v>20330051920318</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920335</v>
+        <v>20330050470026</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920318</v>
+        <v>20330051920320</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
         <v>97</v>
@@ -3112,13 +3012,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330050470026</v>
+        <v>20330051920321</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="D9" t="s">
         <v>98</v>
@@ -3129,13 +3029,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920320</v>
+        <v>20330051920322</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
         <v>99</v>
@@ -3146,13 +3046,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920321</v>
+        <v>20330051920323</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
         <v>100</v>
@@ -3163,13 +3063,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920322</v>
+        <v>20330051920380</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
         <v>101</v>
@@ -3180,13 +3080,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920323</v>
+        <v>20330051920324</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
         <v>102</v>
@@ -3197,13 +3097,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920380</v>
+        <v>20330051920325</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
         <v>103</v>
@@ -3214,13 +3114,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920324</v>
+        <v>20330051920397</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
         <v>104</v>
@@ -3231,13 +3131,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920325</v>
+        <v>20330051920326</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="D16" t="s">
         <v>105</v>
@@ -3248,13 +3148,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920326</v>
+        <v>20330051920327</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="D17" t="s">
         <v>106</v>
@@ -3265,13 +3165,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920327</v>
+        <v>20330051920396</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
         <v>107</v>
@@ -3282,13 +3182,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920396</v>
+        <v>20330051920329</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D19" t="s">
         <v>108</v>
@@ -3299,13 +3199,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920329</v>
+        <v>17330051920191</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D20" t="s">
         <v>109</v>
@@ -3316,13 +3216,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>17330051920191</v>
+        <v>20330051920331</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D21" t="s">
         <v>110</v>
@@ -3333,13 +3233,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920331</v>
+        <v>20330051920333</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D22" t="s">
         <v>111</v>
@@ -3350,13 +3250,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920333</v>
+        <v>20330051920335</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D23" t="s">
         <v>112</v>
@@ -3372,7 +3272,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3404,22 +3304,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920320</v>
+        <v>20330051920325</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
         <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -3427,19 +3327,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920320</v>
+        <v>20330051920325</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
         <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>44</v>
@@ -3450,13 +3350,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920325</v>
+        <v>20330051920326</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
         <v>105</v>
@@ -3465,7 +3365,7 @@
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -3473,22 +3373,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920325</v>
+        <v>20330051920326</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
         <v>105</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -3496,19 +3396,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920326</v>
+        <v>20330051920320</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
         <v>43</v>
@@ -3519,19 +3419,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920326</v>
+        <v>20330051920329</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>44</v>
@@ -3542,70 +3442,24 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920396</v>
+        <v>17330051920191</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920329</v>
-      </c>
-      <c r="B9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D9" t="s">
-        <v>109</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>17330051920191</v>
-      </c>
-      <c r="B10" t="s">
-        <v>83</v>
-      </c>
-      <c r="C10" t="s">
-        <v>94</v>
-      </c>
-      <c r="D10" t="s">
-        <v>110</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ASV - Estadisticos 20211.xlsx
+++ b/grupos/3ASV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="113">
   <si>
     <t>Materia</t>
   </si>
@@ -149,24 +149,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
+  </si>
+  <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
+    <t>Acevedo Rendón Ismael Arturo</t>
+  </si>
+  <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
-  </si>
-  <si>
     <t>Camarillo Aburto Raymundo</t>
   </si>
   <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -182,178 +182,178 @@
     <t>APALE</t>
   </si>
   <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>CANTELLAN</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GAMEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MAYA</t>
+  </si>
+  <si>
     <t>MOLINA</t>
   </si>
   <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
     <t>OCAÑA</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
     <t>ESTEVEZ</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>TEPEPA</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>SILVERIO</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>TLAXCALA</t>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>TZIZIHUA</t>
   </si>
   <si>
     <t>JOSE MIGUEL</t>
   </si>
   <si>
+    <t>GUILLERMO SAID</t>
+  </si>
+  <si>
+    <t>DIANA ITZEL</t>
+  </si>
+  <si>
+    <t>DANIELA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>SURISADAY</t>
+  </si>
+  <si>
+    <t>MARCOS</t>
+  </si>
+  <si>
+    <t>JESUS SAMUEL</t>
+  </si>
+  <si>
+    <t>ROGELIO</t>
+  </si>
+  <si>
+    <t>ARIZBETH</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>JESUS ANTONIO</t>
+  </si>
+  <si>
+    <t>FRANCISCO YAEL</t>
+  </si>
+  <si>
     <t>IRVING</t>
   </si>
   <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>JUAN GUILLERMO</t>
+  </si>
+  <si>
     <t>OZIEL</t>
   </si>
   <si>
+    <t>KELLY ITZEL</t>
+  </si>
+  <si>
+    <t>MICHELLE ROBERTA</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
     <t>JAQUELINE</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>CANTELLAN</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MAYA</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>TEPEPA</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>SILVERIO</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>TZIZIHUA</t>
-  </si>
-  <si>
-    <t>GUILLERMO SAID</t>
-  </si>
-  <si>
-    <t>DIANA ITZEL</t>
-  </si>
-  <si>
-    <t>DANIELA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>SURISADAY</t>
-  </si>
-  <si>
-    <t>MARCOS</t>
-  </si>
-  <si>
-    <t>JESUS SAMUEL</t>
-  </si>
-  <si>
-    <t>ROGELIO</t>
-  </si>
-  <si>
-    <t>ARIZBETH</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>JESUS ANTONIO</t>
-  </si>
-  <si>
-    <t>FRANCISCO YAEL</t>
-  </si>
-  <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>JUAN GUILLERMO</t>
-  </si>
-  <si>
-    <t>KELLY ITZEL</t>
-  </si>
-  <si>
-    <t>MICHELLE ROBERTA</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
   </si>
   <si>
     <t>DORA LUZ</t>
@@ -878,25 +878,25 @@
         <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U4">
         <v>9</v>
@@ -905,13 +905,13 @@
         <v>8</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -925,7 +925,7 @@
         <v>6</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E5">
         <v>6</v>
@@ -943,10 +943,10 @@
         <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>6</v>
@@ -955,37 +955,37 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U5">
         <v>7</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>6</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -1032,22 +1032,22 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>8</v>
@@ -1065,7 +1065,7 @@
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1109,22 +1109,22 @@
         <v>7</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>6</v>
@@ -1133,16 +1133,16 @@
         <v>6</v>
       </c>
       <c r="V7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1174,10 +1174,10 @@
         <v>5</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
         <v>6</v>
@@ -1186,28 +1186,28 @@
         <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T8">
         <v>6</v>
       </c>
       <c r="U8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V8">
         <v>6</v>
@@ -1219,7 +1219,7 @@
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1263,22 +1263,22 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -1296,7 +1296,7 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1340,40 +1340,40 @@
         <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>7</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X10">
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1417,22 +1417,22 @@
         <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>8</v>
@@ -1444,7 +1444,7 @@
         <v>7</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -1482,7 +1482,7 @@
         <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
         <v>8</v>
@@ -1494,25 +1494,25 @@
         <v>7</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>8</v>
@@ -1521,13 +1521,13 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1559,7 +1559,7 @@
         <v>5</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
         <v>6</v>
@@ -1571,37 +1571,37 @@
         <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>6</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1636,10 +1636,10 @@
         <v>5</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>6</v>
@@ -1648,37 +1648,37 @@
         <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U14">
         <v>5</v>
       </c>
       <c r="V14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W14">
         <v>6</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>5</v>
@@ -1725,40 +1725,40 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>8</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1802,22 +1802,22 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T16">
         <v>8</v>
@@ -1835,7 +1835,7 @@
         <v>9</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1855,7 +1855,7 @@
         <v>5</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -1867,49 +1867,49 @@
         <v>5</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>5</v>
@@ -1956,40 +1956,40 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U18">
         <v>7</v>
       </c>
       <c r="V18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2033,25 +2033,25 @@
         <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U19">
         <v>7</v>
@@ -2060,13 +2060,13 @@
         <v>8</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>9</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2080,7 +2080,7 @@
         <v>5</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E20">
         <v>6</v>
@@ -2098,7 +2098,7 @@
         <v>5</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
         <v>6</v>
@@ -2110,37 +2110,37 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U20">
         <v>5</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>6</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>5</v>
@@ -2163,16 +2163,16 @@
         <v>6</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2216,22 +2216,22 @@
         <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>9</v>
@@ -2243,7 +2243,7 @@
         <v>9</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X22">
         <v>10</v>
@@ -2293,40 +2293,40 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>9</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2340,13 +2340,13 @@
         <v>5</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E24">
         <v>5</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G24">
         <v>5</v>
@@ -2358,49 +2358,49 @@
         <v>5</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U24">
         <v>5</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W24">
         <v>5</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -2435,7 +2435,7 @@
         <v>5</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K25">
         <v>6</v>
@@ -2447,31 +2447,31 @@
         <v>5</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W25">
         <v>6</v>
@@ -2536,7 +2536,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>43</v>
@@ -2545,30 +2545,30 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>61.9</v>
+        <v>66.67</v>
       </c>
       <c r="G2">
-        <v>23.81</v>
+        <v>33.33</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>44</v>
@@ -2577,19 +2577,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>61.9</v>
+        <v>76.19</v>
       </c>
       <c r="G3">
-        <v>38.1</v>
+        <v>23.81</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2600,28 +2600,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>45</v>
       </c>
       <c r="C4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>66.67</v>
+        <v>90.91</v>
       </c>
       <c r="G4">
-        <v>33.33</v>
+        <v>9.09</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2632,28 +2632,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>46</v>
       </c>
       <c r="C5">
+        <v>22</v>
+      </c>
+      <c r="D5">
         <v>21</v>
       </c>
-      <c r="D5">
-        <v>17</v>
-      </c>
       <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>80.95</v>
+        <v>95.45</v>
       </c>
       <c r="G5">
-        <v>19.05</v>
+        <v>4.55</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2664,28 +2664,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>47</v>
       </c>
       <c r="C6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>86.36</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>13.64</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2696,34 +2696,34 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>48</v>
       </c>
       <c r="C7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>90.91</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>7.1</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2733,7 +2733,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2758,106 +2758,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920317</v>
-      </c>
-      <c r="B2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920328</v>
-      </c>
-      <c r="B3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920330</v>
-      </c>
-      <c r="B4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920334</v>
-      </c>
-      <c r="B5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920334</v>
-      </c>
-      <c r="B6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -2893,81 +2793,81 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920334</v>
+        <v>20330051920317</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920317</v>
+        <v>20330051920318</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920328</v>
+        <v>20330050470026</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920330</v>
+        <v>20330051920320</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920318</v>
+        <v>20330051920321</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
         <v>95</v>
@@ -2978,13 +2878,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330050470026</v>
+        <v>20330051920322</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
         <v>96</v>
@@ -2995,13 +2895,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920320</v>
+        <v>20330051920323</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
         <v>97</v>
@@ -3012,13 +2912,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920321</v>
+        <v>20330051920380</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
         <v>98</v>
@@ -3029,13 +2929,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920322</v>
+        <v>20330051920324</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="D10" t="s">
         <v>99</v>
@@ -3046,13 +2946,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920323</v>
+        <v>20330051920325</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
         <v>100</v>
@@ -3063,13 +2963,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920380</v>
+        <v>20330051920397</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
         <v>101</v>
@@ -3080,13 +2980,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920324</v>
+        <v>20330051920326</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
         <v>102</v>
@@ -3097,13 +2997,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920325</v>
+        <v>20330051920327</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="D14" t="s">
         <v>103</v>
@@ -3114,13 +3014,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920397</v>
+        <v>20330051920328</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D15" t="s">
         <v>104</v>
@@ -3131,13 +3031,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920326</v>
+        <v>20330051920396</v>
       </c>
       <c r="B16" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="D16" t="s">
         <v>105</v>
@@ -3148,13 +3048,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920327</v>
+        <v>20330051920329</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="D17" t="s">
         <v>106</v>
@@ -3165,13 +3065,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920396</v>
+        <v>20330051920330</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D18" t="s">
         <v>107</v>
@@ -3182,13 +3082,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920329</v>
+        <v>17330051920191</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D19" t="s">
         <v>108</v>
@@ -3199,13 +3099,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>17330051920191</v>
+        <v>20330051920331</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D20" t="s">
         <v>109</v>
@@ -3216,13 +3116,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920331</v>
+        <v>20330051920333</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C21" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D21" t="s">
         <v>110</v>
@@ -3233,13 +3133,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920333</v>
+        <v>20330051920334</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C22" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="D22" t="s">
         <v>111</v>
@@ -3253,10 +3153,10 @@
         <v>20330051920335</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C23" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D23" t="s">
         <v>112</v>
@@ -3272,7 +3172,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3304,22 +3204,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920325</v>
+        <v>20330051920397</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -3327,22 +3227,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920325</v>
+        <v>20330051920397</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -3350,22 +3250,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920326</v>
+        <v>20330051920328</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -3373,19 +3273,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920326</v>
+        <v>20330051920328</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
         <v>43</v>
@@ -3396,22 +3296,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920320</v>
+        <v>20330051920330</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -3419,22 +3319,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920329</v>
+        <v>20330051920330</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -3442,24 +3342,116 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>17330051920191</v>
+        <v>20330051920317</v>
       </c>
       <c r="B8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920321</v>
+      </c>
+      <c r="B9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" t="s">
         <v>78</v>
       </c>
-      <c r="C8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D8" t="s">
-        <v>109</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8">
+      <c r="D9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920325</v>
+      </c>
+      <c r="B10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" t="s">
+        <v>100</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920396</v>
+      </c>
+      <c r="B11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920335</v>
+      </c>
+      <c r="B12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" t="s">
+        <v>112</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12">
         <v>5</v>
       </c>
     </row>
